--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.30837467240169</v>
+        <v>6.875110884265275</v>
       </c>
       <c r="D2" t="n">
-        <v>42.02170769903503</v>
+        <v>6.828527501093192</v>
       </c>
       <c r="E2" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F2" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.82796387110061</v>
+        <v>8.747044129053851</v>
       </c>
       <c r="D3" t="n">
-        <v>53.7584530872231</v>
+        <v>8.735748626673754</v>
       </c>
       <c r="E3" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F3" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.7770713922319</v>
+        <v>9.713774101237684</v>
       </c>
       <c r="D4" t="n">
-        <v>59.80752119116237</v>
+        <v>9.718722193563886</v>
       </c>
       <c r="E4" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F4" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>69.54555005579273</v>
+        <v>11.30115188406632</v>
       </c>
       <c r="D5" t="n">
-        <v>68.93767965679689</v>
+        <v>11.2023729442295</v>
       </c>
       <c r="E5" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F5" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.11694285204489</v>
+        <v>8.631503213457295</v>
       </c>
       <c r="D6" t="n">
-        <v>52.53446240990138</v>
+        <v>8.536850141608975</v>
       </c>
       <c r="E6" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F6" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.61120732599634</v>
+        <v>7.411821190474406</v>
       </c>
       <c r="D7" t="n">
-        <v>45.79698375825952</v>
+        <v>7.442009860717173</v>
       </c>
       <c r="E7" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F7" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.28238295555605</v>
+        <v>1.670887230277857</v>
       </c>
       <c r="D8" t="n">
-        <v>9.671068692025891</v>
+        <v>1.571548662454207</v>
       </c>
       <c r="E8" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F8" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.11780548500926</v>
+        <v>3.431643391314004</v>
       </c>
       <c r="D9" t="n">
-        <v>20.61554341012844</v>
+        <v>3.350025804145872</v>
       </c>
       <c r="E9" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F9" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.08474503829861</v>
+        <v>6.188771068723524</v>
       </c>
       <c r="D10" t="n">
-        <v>38.62533206289079</v>
+        <v>6.276616460219754</v>
       </c>
       <c r="E10" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F10" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.20313559581703</v>
+        <v>5.070509534320268</v>
       </c>
       <c r="D11" t="n">
-        <v>31.08526714941463</v>
+        <v>5.051355911779878</v>
       </c>
       <c r="E11" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F11" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.29239366310604</v>
+        <v>4.597513970254731</v>
       </c>
       <c r="D12" t="n">
-        <v>28.92132592699324</v>
+        <v>4.699715463136402</v>
       </c>
       <c r="E12" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F12" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.84507444294373</v>
+        <v>7.937324596978356</v>
       </c>
       <c r="D13" t="n">
-        <v>49.42927956740313</v>
+        <v>8.032257929703009</v>
       </c>
       <c r="E13" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F13" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.55374275590987</v>
+        <v>7.077483197835354</v>
       </c>
       <c r="D14" t="n">
-        <v>43.5410295933286</v>
+        <v>7.075417308915897</v>
       </c>
       <c r="E14" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F14" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>58.36834279641403</v>
+        <v>9.484855704417281</v>
       </c>
       <c r="D15" t="n">
-        <v>59.00872621667398</v>
+        <v>9.588918010209522</v>
       </c>
       <c r="E15" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F15" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>58.02658426646646</v>
+        <v>9.429319943300801</v>
       </c>
       <c r="D16" t="n">
-        <v>58.66952870746121</v>
+        <v>9.533798414962448</v>
       </c>
       <c r="E16" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F16" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>54.92589530976239</v>
+        <v>8.925457987836388</v>
       </c>
       <c r="D17" t="n">
-        <v>55.20173017545042</v>
+        <v>8.970281153510694</v>
       </c>
       <c r="E17" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F17" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>62.44764658324026</v>
+        <v>10.14774256977654</v>
       </c>
       <c r="D18" t="n">
-        <v>62.92454429018454</v>
+        <v>10.22523844715499</v>
       </c>
       <c r="E18" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F18" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>101.7856915164708</v>
+        <v>16.5401748714265</v>
       </c>
       <c r="D19" t="n">
-        <v>102.2577060303402</v>
+        <v>16.61687722993029</v>
       </c>
       <c r="E19" t="n">
-        <v>19.68798896754201</v>
+        <v>3.199298207225576</v>
       </c>
       <c r="F19" t="n">
-        <v>19.83953953636764</v>
+        <v>3.223925174659741</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
